--- a/output/pdf_financials_xlsx/SKP.xlsx
+++ b/output/pdf_financials_xlsx/SKP.xlsx
@@ -5987,40 +5987,40 @@
         <v>4.621913</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.877281</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.232501</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.575865</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.156406</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.524304</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.073703999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>9.009739</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>10.220674</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.290884</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.630001</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>11.393613</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>11.749879</v>
       </c>
     </row>
     <row r="93">
@@ -9554,7 +9554,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -10574,7 +10578,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11679,7 +11687,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12570,7 +12582,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13255,7 +13271,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13835,7 +13855,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -14536,7 +14560,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -14841,7 +14869,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -15146,7 +15178,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -15451,7 +15487,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SKP.xlsx
+++ b/output/pdf_financials_xlsx/SKP.xlsx
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002704</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>-0.004034</v>
@@ -1052,37 +1052,37 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000246</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>9.3e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003458</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.026515</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.058893</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000968</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004141</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.005052</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000705</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.076353</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.089347</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>-1.552997</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.383716</v>
+        <v>-1.38642</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.28557</v>
@@ -2014,37 +2014,37 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.789748</v>
+        <v>-0.789994</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.194914</v>
+        <v>-1.195007</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.076292</v>
+        <v>-1.07975</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-8.374205999999999</v>
+        <v>-8.400721000000001</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-8.199919</v>
+        <v>-8.258812000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.961203</v>
+        <v>-3.962171</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.684956</v>
+        <v>-3.689097</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.252261</v>
+        <v>-5.257313</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.129111</v>
+        <v>-1.129816</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.486993</v>
+        <v>-3.563346</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-4.671354</v>
+        <v>-4.760701</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-2.340294</v>
@@ -2118,7 +2118,7 @@
         <v>-1.552997</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.383716</v>
+        <v>-1.38642</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.27846</v>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.789748</v>
+        <v>-0.789994</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.194914</v>
+        <v>-1.195007</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.076292</v>
+        <v>-1.07975</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-8.374205999999999</v>
+        <v>-8.400721000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-8.199919</v>
+        <v>-8.258812000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.961203</v>
+        <v>-3.962171</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.684956</v>
+        <v>-3.689097</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.252261</v>
+        <v>-5.257313</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.129111</v>
+        <v>-1.129816</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.486993</v>
+        <v>-3.563346</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.671354</v>
+        <v>-4.760701</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-2.340294</v>
@@ -2430,28 +2430,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.161002</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.230471</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.230471</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.072433</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.081647</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.365216</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.146441</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.935655</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>1.400473</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.950674</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>3.245492</v>
       </c>
     </row>
     <row r="35">
@@ -2546,28 +2546,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.161002</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7.230471</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.14308</v>
+        <v>9.373551000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.14308</v>
+        <v>2.215513</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.081647</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.365216</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.146441</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.935655</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0</v>
@@ -2591,10 +2591,10 @@
         <v>1.400473</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.950674</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>3.245492</v>
       </c>
     </row>
     <row r="37">
@@ -3242,28 +3242,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.184276</v>
+        <v>0.023274</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>7.374289</v>
+        <v>0.143818</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.231209</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.558073</v>
+        <v>1.476426</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.369258</v>
+        <v>0.004042</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.147995</v>
+        <v>0.001554</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.938709</v>
+        <v>0.003054</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>5.394663</v>
@@ -3287,10 +3287,10 @@
         <v>0.125805</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.368878</v>
+        <v>0.418204</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.364086</v>
+        <v>0.118594</v>
       </c>
     </row>
     <row r="49">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -16820,7 +16820,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -47996,7 +47996,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -50940,7 +50940,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -55738,7 +55738,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -56647,7 +56647,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -57356,7 +57356,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -60269,7 +60269,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -60768,7 +60768,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -61770,7 +61770,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E531" s="5" t="n">

--- a/output/pdf_financials_xlsx/SKP.xlsx
+++ b/output/pdf_financials_xlsx/SKP.xlsx
@@ -7600,13 +7600,13 @@
         <v>0.05</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>1.2875</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>0</v>
+        <v>3.684765</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>7.560984</v>
       </c>
       <c r="N120" s="3" t="n">
         <v>0</v>
@@ -31842,7 +31842,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -32937,7 +32941,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SKP.xlsx
+++ b/output/pdf_financials_xlsx/SKP.xlsx
@@ -4433,40 +4433,40 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.032325</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.025902</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.21625</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.267668</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.477778</v>
       </c>
     </row>
     <row r="68">
@@ -7047,13 +7047,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004308</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.127059</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7062,10 +7062,10 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000674</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00134</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
         <v>0.229723</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.692837</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.214608</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -7312,22 +7312,22 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.748048</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.066945</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>1.540494</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>1.465103</v>
       </c>
     </row>
     <row r="116">
@@ -8419,13 +8419,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004308</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.127059</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8434,10 +8434,10 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000674</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00134</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.405144</v>
+        <v>-3.532203</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.3993</v>
@@ -8496,10 +8496,10 @@
         <v>-1.33294</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.49934</v>
+        <v>-0.500014</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.657435</v>
+        <v>-0.658775</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.461136</v>
@@ -21977,7 +21977,11 @@
           <t>Proceeds from sale of marketable securities 5</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -22989,7 +22993,11 @@
           <t>Fair value of broker warrants issued in connection with private placement $</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -23090,7 +23098,11 @@
           <t>Residual value of warrants issued on private placement $</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -24698,7 +24710,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -27993,7 +28009,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -31638,7 +31658,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -33848,7 +33872,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -36989,7 +37017,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -37908,7 +37940,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -38007,7 +38043,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -41756,7 +41796,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -44192,7 +44236,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E355" s="5" t="n">
         <v>-0.004308</v>
       </c>
